--- a/data/daily/distance.xlsx
+++ b/data/daily/distance.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="251">
   <si>
     <t>Total</t>
   </si>
@@ -22,7 +22,16 @@
     <t>Username</t>
   </si>
   <si>
-    <t>Apr 20, 2026</t>
+    <t>Apr 25, 2026</t>
+  </si>
+  <si>
+    <t>Dillip Kumar Mohanty</t>
+  </si>
+  <si>
+    <t>dillip_st</t>
+  </si>
+  <si>
+    <t>--</t>
   </si>
   <si>
     <t>Pranjal Gupta</t>
@@ -31,9 +40,6 @@
     <t>pranjal_st</t>
   </si>
   <si>
-    <t>--</t>
-  </si>
-  <si>
     <t>Vaibhav Prabhakar Kamble</t>
   </si>
   <si>
@@ -46,7 +52,7 @@
     <t>rajesh_sts</t>
   </si>
   <si>
-    <t>0.15</t>
+    <t>123.57</t>
   </si>
   <si>
     <t>Hemendra Kumar</t>
@@ -67,7 +73,7 @@
     <t>shalaka_sts</t>
   </si>
   <si>
-    <t>19.84</t>
+    <t>0.16</t>
   </si>
   <si>
     <t>Satwinder Pal Jagotra</t>
@@ -88,6 +94,9 @@
     <t>manas_shaurrya</t>
   </si>
   <si>
+    <t>28.48</t>
+  </si>
+  <si>
     <t>Hariharan B</t>
   </si>
   <si>
@@ -112,13 +121,16 @@
     <t>ankush_sts</t>
   </si>
   <si>
+    <t>26.58</t>
+  </si>
+  <si>
     <t>Sandeep Kumar Singh</t>
   </si>
   <si>
     <t>sanddepsingh_sts</t>
   </si>
   <si>
-    <t>1.64</t>
+    <t>48.92</t>
   </si>
   <si>
     <t>Sachin Verma</t>
@@ -133,7 +145,7 @@
     <t>piyush_st</t>
   </si>
   <si>
-    <t>66</t>
+    <t>19.41</t>
   </si>
   <si>
     <t>Kalyan Kashinath Pathare</t>
@@ -154,7 +166,7 @@
     <t>dipanshu_st</t>
   </si>
   <si>
-    <t>39.49</t>
+    <t>27.49</t>
   </si>
   <si>
     <t>Amaan Aijaz</t>
@@ -163,7 +175,7 @@
     <t>amaan_st</t>
   </si>
   <si>
-    <t>10.44</t>
+    <t>0.01</t>
   </si>
   <si>
     <t>Sunpreet Singh</t>
@@ -190,7 +202,7 @@
     <t>afsar_st</t>
   </si>
   <si>
-    <t>15.04</t>
+    <t>34.74</t>
   </si>
   <si>
     <t>Sibayan Ghosh</t>
@@ -199,7 +211,7 @@
     <t>sibayan_st</t>
   </si>
   <si>
-    <t>35.45</t>
+    <t>26.84</t>
   </si>
   <si>
     <t>Niranjan M</t>
@@ -208,16 +220,13 @@
     <t>niranjan_sts</t>
   </si>
   <si>
-    <t>34.06</t>
-  </si>
-  <si>
     <t>Sushank Rajendra Mohakar</t>
   </si>
   <si>
     <t>sushank_sts</t>
   </si>
   <si>
-    <t>52.38</t>
+    <t>125.36</t>
   </si>
   <si>
     <t>Satish Megaraj</t>
@@ -226,7 +235,7 @@
     <t>satish_st</t>
   </si>
   <si>
-    <t>25.77</t>
+    <t>84.17</t>
   </si>
   <si>
     <t>Sagar Kanubhai</t>
@@ -235,7 +244,7 @@
     <t>sagark_st</t>
   </si>
   <si>
-    <t>0.05</t>
+    <t>30.82</t>
   </si>
   <si>
     <t>Yogesh Naykodi</t>
@@ -250,7 +259,7 @@
     <t>ishhanque_st</t>
   </si>
   <si>
-    <t>35.86</t>
+    <t>23.39</t>
   </si>
   <si>
     <t>Nilesh K Salunke</t>
@@ -259,7 +268,7 @@
     <t>nilesh_st</t>
   </si>
   <si>
-    <t>5.9</t>
+    <t>7.32</t>
   </si>
   <si>
     <t>Arsadur Rahaman Halder</t>
@@ -268,7 +277,7 @@
     <t>arsadur_st</t>
   </si>
   <si>
-    <t>158.08</t>
+    <t>158.84</t>
   </si>
   <si>
     <t>Kishor Krushna Tegade</t>
@@ -277,7 +286,7 @@
     <t>kishor_st</t>
   </si>
   <si>
-    <t>12.8</t>
+    <t>13.89</t>
   </si>
   <si>
     <t>Mithilesh Mishra</t>
@@ -292,7 +301,7 @@
     <t>vineet_st</t>
   </si>
   <si>
-    <t>136</t>
+    <t>67.36</t>
   </si>
   <si>
     <t>Suyog Laxman Kajare</t>
@@ -301,7 +310,7 @@
     <t>suyog_st</t>
   </si>
   <si>
-    <t>51.47</t>
+    <t>44.63</t>
   </si>
   <si>
     <t>Suresh Gowda</t>
@@ -310,7 +319,7 @@
     <t>suresh_st</t>
   </si>
   <si>
-    <t>43.25</t>
+    <t>79.06</t>
   </si>
   <si>
     <t>Sunil P Bhagwat</t>
@@ -319,7 +328,7 @@
     <t>sunilb_st</t>
   </si>
   <si>
-    <t>85.29</t>
+    <t>28.35</t>
   </si>
   <si>
     <t>Ganesh Bhimsen Kumbhar</t>
@@ -328,7 +337,7 @@
     <t>ganeshk_st</t>
   </si>
   <si>
-    <t>60.25</t>
+    <t>10.79</t>
   </si>
   <si>
     <t>Devendra Pal Singh</t>
@@ -337,16 +346,13 @@
     <t>devendra_st</t>
   </si>
   <si>
-    <t>0.95</t>
-  </si>
-  <si>
     <t>Sagar Deepak Gurav</t>
   </si>
   <si>
     <t>sagar_st</t>
   </si>
   <si>
-    <t>26.58</t>
+    <t>3.65</t>
   </si>
   <si>
     <t>Pradeep  Brahampal Rajoria</t>
@@ -355,7 +361,7 @@
     <t>pradeep_st</t>
   </si>
   <si>
-    <t>37.3</t>
+    <t>32.81</t>
   </si>
   <si>
     <t>Raghvendra Kumar</t>
@@ -364,13 +370,16 @@
     <t>raghvendra_st</t>
   </si>
   <si>
+    <t>135.13</t>
+  </si>
+  <si>
     <t>Sanjeev S Panwar</t>
   </si>
   <si>
     <t>sanjeev_st</t>
   </si>
   <si>
-    <t>34.88</t>
+    <t>272.73</t>
   </si>
   <si>
     <t>Sachin Mahade</t>
@@ -379,7 +388,7 @@
     <t>sachin_st</t>
   </si>
   <si>
-    <t>43.59</t>
+    <t>31.56</t>
   </si>
   <si>
     <t>RATAN BAHADHUR SINGH</t>
@@ -388,7 +397,7 @@
     <t>ratan_st</t>
   </si>
   <si>
-    <t>24.27</t>
+    <t>25.74</t>
   </si>
   <si>
     <t>Rajnish Nimbark</t>
@@ -397,7 +406,7 @@
     <t>rajnish_st</t>
   </si>
   <si>
-    <t>64.58</t>
+    <t>20.12</t>
   </si>
   <si>
     <t>Pankaj Chaudhary</t>
@@ -406,7 +415,7 @@
     <t>pankaj_st</t>
   </si>
   <si>
-    <t>12.4</t>
+    <t>0.04</t>
   </si>
   <si>
     <t>Karim Khan</t>
@@ -415,7 +424,7 @@
     <t>karim_st</t>
   </si>
   <si>
-    <t>33.45</t>
+    <t>27.18</t>
   </si>
   <si>
     <t>Irrappa Bassapa</t>
@@ -424,7 +433,7 @@
     <t>irrappa_st</t>
   </si>
   <si>
-    <t>65.36</t>
+    <t>60.78</t>
   </si>
   <si>
     <t>Gopal  Sonkar</t>
@@ -433,7 +442,7 @@
     <t>gopal_st</t>
   </si>
   <si>
-    <t>13.58</t>
+    <t>31.06</t>
   </si>
   <si>
     <t>Dattatray Ganpat Ranmakar</t>
@@ -442,7 +451,7 @@
     <t>dattatray_st</t>
   </si>
   <si>
-    <t>19.28</t>
+    <t>13.57</t>
   </si>
   <si>
     <t>Badhan Sarkar</t>
@@ -457,7 +466,7 @@
     <t>ashok_st</t>
   </si>
   <si>
-    <t>5.69</t>
+    <t>125.87</t>
   </si>
   <si>
     <t>Ankaj Chaudhary</t>
@@ -472,7 +481,7 @@
     <t>akhilesh_st</t>
   </si>
   <si>
-    <t>24.31</t>
+    <t>26.06</t>
   </si>
   <si>
     <t>Adesh Kumar Patel</t>
@@ -481,7 +490,7 @@
     <t>adesh_st</t>
   </si>
   <si>
-    <t>56.63</t>
+    <t>2.17</t>
   </si>
   <si>
     <t>Saurabh Gupta</t>
@@ -490,13 +499,16 @@
     <t>saurabh_st</t>
   </si>
   <si>
+    <t>5.39</t>
+  </si>
+  <si>
     <t>RUPESH YASHWANT RANE</t>
   </si>
   <si>
     <t>rupesh_st</t>
   </si>
   <si>
-    <t>98.35</t>
+    <t>35.77</t>
   </si>
   <si>
     <t>Anish Kumar</t>
@@ -505,7 +517,7 @@
     <t>anish_st</t>
   </si>
   <si>
-    <t>31.14</t>
+    <t>79.45</t>
   </si>
   <si>
     <t>Shivanshu Dubey</t>
@@ -514,7 +526,7 @@
     <t>shivanshu_st</t>
   </si>
   <si>
-    <t>4.9</t>
+    <t>0</t>
   </si>
   <si>
     <t>Prabhakar Gopalrao Gaikwad</t>
@@ -523,7 +535,7 @@
     <t>prabhakar_st</t>
   </si>
   <si>
-    <t>72.67</t>
+    <t>11.99</t>
   </si>
   <si>
     <t>Azeem Khan</t>
@@ -538,7 +550,7 @@
     <t>kuljeet_st</t>
   </si>
   <si>
-    <t>12.62</t>
+    <t>34.63</t>
   </si>
   <si>
     <t>Shabbir Khan</t>
@@ -547,7 +559,7 @@
     <t>shabbir_st</t>
   </si>
   <si>
-    <t>70.58</t>
+    <t>32.38</t>
   </si>
   <si>
     <t>Abhiman Ganguly</t>
@@ -556,7 +568,7 @@
     <t>abhiman_st</t>
   </si>
   <si>
-    <t>30.64</t>
+    <t>23.92</t>
   </si>
   <si>
     <t>Test</t>
@@ -1164,7 +1176,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D101"/>
+  <dimension ref="A1:D102"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" defaultColWidth="20"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1211,7 +1223,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>9</v>
@@ -1220,21 +1232,21 @@
         <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
-        <v>0</v>
+        <v>123.57</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>13</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1253,7 +1265,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
-        <v>19.84</v>
+        <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>16</v>
@@ -1262,21 +1274,21 @@
         <v>17</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1309,7 +1321,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
-        <v>0</v>
+        <v>28.48</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>25</v>
@@ -1318,7 +1330,7 @@
         <v>26</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1326,10 +1338,10 @@
         <v>0</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>6</v>
@@ -1340,10 +1352,10 @@
         <v>0</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>6</v>
@@ -1354,10 +1366,10 @@
         <v>0</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>6</v>
@@ -1365,58 +1377,58 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
-        <v>1.64</v>
+        <v>26.58</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>0</v>
+        <v>48.92</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>6</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>40</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>0</v>
+        <v>19.41</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1424,10 +1436,10 @@
         <v>0</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>6</v>
@@ -1435,44 +1447,44 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>39.49</v>
+        <v>0</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>47</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
-        <v>10.44</v>
+        <v>27.49</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>6</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1480,10 +1492,10 @@
         <v>0</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>6</v>
@@ -1494,10 +1506,10 @@
         <v>0</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>6</v>
@@ -1505,63 +1517,63 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
-        <v>15.04</v>
+        <v>0</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>59</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
-        <v>35.45</v>
+        <v>34.74</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
-        <v>34.06</v>
+        <v>26.84</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
-        <v>52.38</v>
+        <v>0</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>68</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
-        <v>25.77</v>
+        <v>125.36</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>69</v>
@@ -1575,7 +1587,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
-        <v>0.05</v>
+        <v>84.17</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>72</v>
@@ -1589,7 +1601,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
-        <v>0</v>
+        <v>30.82</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>75</v>
@@ -1598,26 +1610,26 @@
         <v>76</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
-        <v>35.86</v>
+        <v>0</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>79</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
-        <v>5.9</v>
+        <v>23.39</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>80</v>
@@ -1631,7 +1643,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
-        <v>158.08</v>
+        <v>7.32</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>83</v>
@@ -1645,7 +1657,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
-        <v>12.8</v>
+        <v>158.84</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>86</v>
@@ -1659,7 +1671,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
-        <v>0</v>
+        <v>13.89</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>89</v>
@@ -1668,26 +1680,26 @@
         <v>90</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>6</v>
+        <v>91</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>93</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
-        <v>51.47</v>
+        <v>67.36</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>94</v>
@@ -1701,7 +1713,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
-        <v>43.25</v>
+        <v>44.63</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>97</v>
@@ -1715,7 +1727,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
-        <v>85.29</v>
+        <v>79.06</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>100</v>
@@ -1729,7 +1741,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
-        <v>60.25</v>
+        <v>28.35</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>103</v>
@@ -1743,7 +1755,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
-        <v>0.95</v>
+        <v>10.79</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>106</v>
@@ -1757,7 +1769,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
-        <v>26.58</v>
+        <v>0</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>109</v>
@@ -1766,40 +1778,40 @@
         <v>110</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>111</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
-        <v>37.3</v>
+        <v>3.65</v>
       </c>
       <c r="B44" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="D44" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
-        <v>0</v>
+        <v>32.81</v>
       </c>
       <c r="B45" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="D45" s="3" t="s">
         <v>116</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
-        <v>34.88</v>
+        <v>135.13</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>117</v>
@@ -1813,7 +1825,7 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
-        <v>43.59</v>
+        <v>272.73</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>120</v>
@@ -1827,7 +1839,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
-        <v>24.27</v>
+        <v>31.56</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>123</v>
@@ -1841,7 +1853,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
-        <v>64.58</v>
+        <v>25.74</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>126</v>
@@ -1855,7 +1867,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
-        <v>12.4</v>
+        <v>20.12</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>129</v>
@@ -1869,7 +1881,7 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
-        <v>33.45</v>
+        <v>0.04</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>132</v>
@@ -1883,7 +1895,7 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
-        <v>65.36</v>
+        <v>27.18</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>135</v>
@@ -1897,7 +1909,7 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
-        <v>13.58</v>
+        <v>60.78</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>138</v>
@@ -1911,7 +1923,7 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
-        <v>19.28</v>
+        <v>31.06</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>141</v>
@@ -1925,7 +1937,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
-        <v>0</v>
+        <v>13.57</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>144</v>
@@ -1934,26 +1946,26 @@
         <v>145</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>6</v>
+        <v>146</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
-        <v>5.69</v>
+        <v>0</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>148</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
-        <v>0</v>
+        <v>125.87</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>149</v>
@@ -1962,26 +1974,26 @@
         <v>150</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>6</v>
+        <v>151</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
-        <v>24.31</v>
+        <v>0</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>153</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
-        <v>56.63</v>
+        <v>26.06</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>154</v>
@@ -1995,7 +2007,7 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
-        <v>85.29</v>
+        <v>2.17</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>157</v>
@@ -2004,133 +2016,133 @@
         <v>158</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>102</v>
+        <v>159</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
-        <v>98.35</v>
+        <v>5.39</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
-        <v>31.14</v>
+        <v>35.77</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
-        <v>4.9</v>
+        <v>79.45</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
-        <v>72.67</v>
+        <v>0</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
-        <v>0</v>
+        <v>11.99</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>6</v>
+        <v>174</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
-        <v>12.62</v>
+        <v>0</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>175</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
-        <v>70.58</v>
+        <v>34.63</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
-        <v>30.64</v>
+        <v>32.38</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
-        <v>0</v>
+        <v>23.92</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>6</v>
+        <v>185</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -2138,10 +2150,10 @@
         <v>0</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>6</v>
@@ -2152,10 +2164,10 @@
         <v>0</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>6</v>
@@ -2166,10 +2178,10 @@
         <v>0</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>6</v>
@@ -2180,10 +2192,10 @@
         <v>0</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>6</v>
@@ -2194,10 +2206,10 @@
         <v>0</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>6</v>
@@ -2208,10 +2220,10 @@
         <v>0</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>6</v>
@@ -2222,10 +2234,10 @@
         <v>0</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>6</v>
@@ -2236,10 +2248,10 @@
         <v>0</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>6</v>
@@ -2250,10 +2262,10 @@
         <v>0</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>6</v>
@@ -2264,10 +2276,10 @@
         <v>0</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>6</v>
@@ -2278,10 +2290,10 @@
         <v>0</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>6</v>
@@ -2292,10 +2304,10 @@
         <v>0</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>6</v>
@@ -2306,10 +2318,10 @@
         <v>0</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>6</v>
@@ -2320,10 +2332,10 @@
         <v>0</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>6</v>
@@ -2334,10 +2346,10 @@
         <v>0</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>6</v>
@@ -2348,10 +2360,10 @@
         <v>0</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>6</v>
@@ -2362,10 +2374,10 @@
         <v>0</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>6</v>
@@ -2376,10 +2388,10 @@
         <v>0</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>6</v>
@@ -2390,10 +2402,10 @@
         <v>0</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>6</v>
@@ -2404,10 +2416,10 @@
         <v>0</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>6</v>
@@ -2418,10 +2430,10 @@
         <v>0</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>6</v>
@@ -2432,10 +2444,10 @@
         <v>0</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>6</v>
@@ -2446,10 +2458,10 @@
         <v>0</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>6</v>
@@ -2460,10 +2472,10 @@
         <v>0</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>6</v>
@@ -2474,10 +2486,10 @@
         <v>0</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>6</v>
@@ -2488,10 +2500,10 @@
         <v>0</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>6</v>
@@ -2502,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>6</v>
@@ -2516,10 +2528,10 @@
         <v>0</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>6</v>
@@ -2530,10 +2542,10 @@
         <v>0</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>6</v>
@@ -2544,10 +2556,10 @@
         <v>0</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>6</v>
@@ -2558,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>6</v>
@@ -2572,12 +2584,26 @@
         <v>0</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D101" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" s="2">
+        <v>0</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D102" s="2" t="s">
         <v>6</v>
       </c>
     </row>
